--- a/backend/data/financials_by_company/1873.HK.xlsx
+++ b/backend/data/financials_by_company/1873.HK.xlsx
@@ -662,586 +662,586 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>11214320.055461</v>
+        <v>9118645.724344</v>
       </c>
       <c r="C2" t="n">
-        <v>0.249296</v>
+        <v>0.135579</v>
       </c>
       <c r="D2" t="n">
-        <v>518474000</v>
+        <v>616706000</v>
       </c>
       <c r="E2" t="n">
-        <v>44984000</v>
+        <v>67257000</v>
       </c>
       <c r="F2" t="n">
-        <v>44984000</v>
+        <v>67257000</v>
       </c>
       <c r="G2" t="n">
-        <v>167294000</v>
+        <v>287546000</v>
       </c>
       <c r="H2" t="n">
-        <v>213861000</v>
+        <v>153154000</v>
       </c>
       <c r="I2" t="n">
-        <v>1299252000</v>
+        <v>1453102000</v>
       </c>
       <c r="J2" t="n">
-        <v>563458000</v>
+        <v>683963000</v>
       </c>
       <c r="K2" t="n">
-        <v>349597000</v>
+        <v>530809000</v>
       </c>
       <c r="L2" t="n">
-        <v>-33353000</v>
+        <v>-156533000</v>
       </c>
       <c r="M2" t="n">
-        <v>53892000</v>
+        <v>183108000</v>
       </c>
       <c r="N2" t="n">
-        <v>20539000</v>
+        <v>26575000</v>
       </c>
       <c r="O2" t="n">
-        <v>133524320.055461</v>
+        <v>229407645.724344</v>
       </c>
       <c r="P2" t="n">
-        <v>167294000</v>
+        <v>287546000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1717062000</v>
+        <v>1834249000</v>
       </c>
       <c r="R2" t="n">
-        <v>2868364000</v>
+        <v>1970799000</v>
       </c>
       <c r="S2" t="n">
-        <v>2136664000</v>
+        <v>1911530000</v>
       </c>
       <c r="T2" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="V2" t="n">
-        <v>167294000</v>
+        <v>162804000</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>-124742000</v>
       </c>
       <c r="X2" t="n">
-        <v>167294000</v>
+        <v>287546000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>167294000</v>
+        <v>287546000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-54693000</v>
+        <v>-13014000</v>
       </c>
       <c r="AB2" t="n">
-        <v>221987000</v>
+        <v>300560000</v>
       </c>
       <c r="AC2" t="n">
-        <v>221987000</v>
+        <v>300560000</v>
       </c>
       <c r="AD2" t="n">
-        <v>73718000</v>
+        <v>47141000</v>
       </c>
       <c r="AE2" t="n">
-        <v>295705000</v>
+        <v>347701000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1599000</v>
+        <v>135729000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-46136000</v>
+        <v>781000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1907000</v>
+        <v>-4291000</v>
       </c>
       <c r="AI2" t="n">
-        <v>44229000</v>
+        <v>3510000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-33353000</v>
+        <v>-156533000</v>
       </c>
       <c r="AK2" t="n">
-        <v>53892000</v>
+        <v>183108000</v>
       </c>
       <c r="AL2" t="n">
-        <v>20539000</v>
+        <v>26575000</v>
       </c>
       <c r="AM2" t="n">
-        <v>269589000</v>
+        <v>269834000</v>
       </c>
       <c r="AN2" t="n">
-        <v>417810000</v>
+        <v>381147000</v>
       </c>
       <c r="AO2" t="n">
-        <v>87986000</v>
+        <v>92382000</v>
       </c>
       <c r="AP2" t="n">
-        <v>364122000</v>
+        <v>320285000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>112233000</v>
+        <v>93974000</v>
       </c>
       <c r="AR2" t="n">
-        <v>251889000</v>
+        <v>226311000</v>
       </c>
       <c r="AS2" t="n">
-        <v>687399000</v>
+        <v>650981000</v>
       </c>
       <c r="AT2" t="n">
-        <v>1299252000</v>
+        <v>1453102000</v>
       </c>
       <c r="AU2" t="n">
-        <v>1986651000</v>
+        <v>2104083000</v>
       </c>
       <c r="AV2" t="n">
-        <v>1986651000</v>
+        <v>2104083000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-55085100</v>
+        <v>-96958050</v>
       </c>
       <c r="C3" t="n">
         <v>0.21</v>
       </c>
       <c r="D3" t="n">
-        <v>594155000</v>
+        <v>372668000</v>
       </c>
       <c r="E3" t="n">
-        <v>-262310000</v>
+        <v>-461705000</v>
       </c>
       <c r="F3" t="n">
-        <v>-262310000</v>
+        <v>-461705000</v>
       </c>
       <c r="G3" t="n">
-        <v>-116113000</v>
+        <v>-528475000</v>
       </c>
       <c r="H3" t="n">
-        <v>211216000</v>
+        <v>185454000</v>
       </c>
       <c r="I3" t="n">
-        <v>1417146000</v>
+        <v>1563952000</v>
       </c>
       <c r="J3" t="n">
-        <v>331845000</v>
+        <v>-89037000</v>
       </c>
       <c r="K3" t="n">
-        <v>120629000</v>
+        <v>-274491000</v>
       </c>
       <c r="L3" t="n">
-        <v>-149207000</v>
+        <v>-163068000</v>
       </c>
       <c r="M3" t="n">
-        <v>176582000</v>
+        <v>184674000</v>
       </c>
       <c r="N3" t="n">
-        <v>27375000</v>
+        <v>21606000</v>
       </c>
       <c r="O3" t="n">
-        <v>91111900</v>
+        <v>-163728050</v>
       </c>
       <c r="P3" t="n">
-        <v>-116113000</v>
+        <v>-528475000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1899453000</v>
+        <v>2067770000</v>
       </c>
       <c r="R3" t="n">
-        <v>2074542857</v>
+        <v>1915437000</v>
       </c>
       <c r="S3" t="n">
-        <v>2028679000</v>
+        <v>1915437000</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.14</v>
+        <v>-0.28</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.06</v>
+        <v>-0.28</v>
       </c>
       <c r="V3" t="n">
-        <v>-290436000</v>
+        <v>-528475000</v>
       </c>
       <c r="W3" t="n">
-        <v>-174323000</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-116113000</v>
+        <v>-528475000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>-116113000</v>
+        <v>-528475000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-16323000</v>
+        <v>-24255000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-99790000</v>
+        <v>-504220000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-99790000</v>
+        <v>-504220000</v>
       </c>
       <c r="AD3" t="n">
-        <v>43837000</v>
+        <v>45055000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-55953000</v>
+        <v>-459165000</v>
       </c>
       <c r="AF3" t="n">
-        <v>164272000</v>
+        <v>138000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-241966000</v>
+        <v>-56588000</v>
       </c>
       <c r="AH3" t="n">
-        <v>222474000</v>
+        <v>40605000</v>
       </c>
       <c r="AI3" t="n">
-        <v>19492000</v>
+        <v>15983000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-149207000</v>
+        <v>-163068000</v>
       </c>
       <c r="AK3" t="n">
-        <v>176582000</v>
+        <v>184674000</v>
       </c>
       <c r="AL3" t="n">
-        <v>27375000</v>
+        <v>21606000</v>
       </c>
       <c r="AM3" t="n">
-        <v>256125000</v>
+        <v>311861000</v>
       </c>
       <c r="AN3" t="n">
-        <v>482307000</v>
+        <v>503818000</v>
       </c>
       <c r="AO3" t="n">
-        <v>127967000</v>
+        <v>135835000</v>
       </c>
       <c r="AP3" t="n">
-        <v>409656000</v>
+        <v>404453000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>132547000</v>
+        <v>130804000</v>
       </c>
       <c r="AR3" t="n">
-        <v>277109000</v>
+        <v>273649000</v>
       </c>
       <c r="AS3" t="n">
-        <v>738432000</v>
+        <v>815679000</v>
       </c>
       <c r="AT3" t="n">
-        <v>1417146000</v>
+        <v>1563952000</v>
       </c>
       <c r="AU3" t="n">
-        <v>2155578000</v>
+        <v>2379631000</v>
       </c>
       <c r="AV3" t="n">
-        <v>2155578000</v>
+        <v>2379631000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-96958050</v>
+        <v>-55085100</v>
       </c>
       <c r="C4" t="n">
         <v>0.21</v>
       </c>
       <c r="D4" t="n">
-        <v>372668000</v>
+        <v>594155000</v>
       </c>
       <c r="E4" t="n">
-        <v>-461705000</v>
+        <v>-262310000</v>
       </c>
       <c r="F4" t="n">
-        <v>-461705000</v>
+        <v>-262310000</v>
       </c>
       <c r="G4" t="n">
-        <v>-528475000</v>
+        <v>-116113000</v>
       </c>
       <c r="H4" t="n">
-        <v>185454000</v>
+        <v>211216000</v>
       </c>
       <c r="I4" t="n">
-        <v>1563952000</v>
+        <v>1417146000</v>
       </c>
       <c r="J4" t="n">
-        <v>-89037000</v>
+        <v>331845000</v>
       </c>
       <c r="K4" t="n">
-        <v>-274491000</v>
+        <v>120629000</v>
       </c>
       <c r="L4" t="n">
-        <v>-163068000</v>
+        <v>-149207000</v>
       </c>
       <c r="M4" t="n">
-        <v>184674000</v>
+        <v>176582000</v>
       </c>
       <c r="N4" t="n">
-        <v>21606000</v>
+        <v>27375000</v>
       </c>
       <c r="O4" t="n">
-        <v>-163728050</v>
+        <v>91111900</v>
       </c>
       <c r="P4" t="n">
-        <v>-528475000</v>
+        <v>-116113000</v>
       </c>
       <c r="Q4" t="n">
-        <v>2067770000</v>
+        <v>1899453000</v>
       </c>
       <c r="R4" t="n">
-        <v>1915437000</v>
+        <v>2074542857</v>
       </c>
       <c r="S4" t="n">
-        <v>1915437000</v>
+        <v>2028679000</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.28</v>
+        <v>-0.14</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.28</v>
+        <v>-0.06</v>
       </c>
       <c r="V4" t="n">
-        <v>-528475000</v>
+        <v>-290436000</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-174323000</v>
       </c>
       <c r="X4" t="n">
-        <v>-528475000</v>
+        <v>-116113000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>-528475000</v>
+        <v>-116113000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-24255000</v>
+        <v>-16323000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-504220000</v>
+        <v>-99790000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-504220000</v>
+        <v>-99790000</v>
       </c>
       <c r="AD4" t="n">
-        <v>45055000</v>
+        <v>43837000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-459165000</v>
+        <v>-55953000</v>
       </c>
       <c r="AF4" t="n">
-        <v>138000</v>
+        <v>164272000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-56588000</v>
+        <v>-241966000</v>
       </c>
       <c r="AH4" t="n">
-        <v>40605000</v>
+        <v>222474000</v>
       </c>
       <c r="AI4" t="n">
-        <v>15983000</v>
+        <v>19492000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-163068000</v>
+        <v>-149207000</v>
       </c>
       <c r="AK4" t="n">
-        <v>184674000</v>
+        <v>176582000</v>
       </c>
       <c r="AL4" t="n">
-        <v>21606000</v>
+        <v>27375000</v>
       </c>
       <c r="AM4" t="n">
-        <v>311861000</v>
+        <v>256125000</v>
       </c>
       <c r="AN4" t="n">
-        <v>503818000</v>
+        <v>482307000</v>
       </c>
       <c r="AO4" t="n">
-        <v>135835000</v>
+        <v>127967000</v>
       </c>
       <c r="AP4" t="n">
-        <v>404453000</v>
+        <v>409656000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>130804000</v>
+        <v>132547000</v>
       </c>
       <c r="AR4" t="n">
-        <v>273649000</v>
+        <v>277109000</v>
       </c>
       <c r="AS4" t="n">
-        <v>815679000</v>
+        <v>738432000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1563952000</v>
+        <v>1417146000</v>
       </c>
       <c r="AU4" t="n">
-        <v>2379631000</v>
+        <v>2155578000</v>
       </c>
       <c r="AV4" t="n">
-        <v>2379631000</v>
+        <v>2155578000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>9118645.724344</v>
+        <v>11214320.055461</v>
       </c>
       <c r="C5" t="n">
-        <v>0.135579</v>
+        <v>0.249296</v>
       </c>
       <c r="D5" t="n">
-        <v>616706000</v>
+        <v>518474000</v>
       </c>
       <c r="E5" t="n">
-        <v>67257000</v>
+        <v>44984000</v>
       </c>
       <c r="F5" t="n">
-        <v>67257000</v>
+        <v>44984000</v>
       </c>
       <c r="G5" t="n">
-        <v>287546000</v>
+        <v>167294000</v>
       </c>
       <c r="H5" t="n">
-        <v>153154000</v>
+        <v>213861000</v>
       </c>
       <c r="I5" t="n">
-        <v>1453102000</v>
+        <v>1299252000</v>
       </c>
       <c r="J5" t="n">
-        <v>683963000</v>
+        <v>563458000</v>
       </c>
       <c r="K5" t="n">
-        <v>530809000</v>
+        <v>349597000</v>
       </c>
       <c r="L5" t="n">
-        <v>-156533000</v>
+        <v>-33353000</v>
       </c>
       <c r="M5" t="n">
-        <v>183108000</v>
+        <v>53892000</v>
       </c>
       <c r="N5" t="n">
-        <v>26575000</v>
+        <v>20539000</v>
       </c>
       <c r="O5" t="n">
-        <v>229407645.724344</v>
+        <v>133524320.055461</v>
       </c>
       <c r="P5" t="n">
-        <v>287546000</v>
+        <v>167294000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1834249000</v>
+        <v>1717062000</v>
       </c>
       <c r="R5" t="n">
-        <v>1970799000</v>
+        <v>2868364000</v>
       </c>
       <c r="S5" t="n">
-        <v>1911530000</v>
+        <v>2136664000</v>
       </c>
       <c r="T5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="U5" t="n">
         <v>0.08</v>
       </c>
-      <c r="U5" t="n">
-        <v>0.15</v>
-      </c>
       <c r="V5" t="n">
-        <v>162804000</v>
+        <v>167294000</v>
       </c>
       <c r="W5" t="n">
-        <v>-124742000</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>287546000</v>
+        <v>167294000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>287546000</v>
+        <v>167294000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-13014000</v>
+        <v>-54693000</v>
       </c>
       <c r="AB5" t="n">
-        <v>300560000</v>
+        <v>221987000</v>
       </c>
       <c r="AC5" t="n">
-        <v>300560000</v>
+        <v>221987000</v>
       </c>
       <c r="AD5" t="n">
-        <v>47141000</v>
+        <v>73718000</v>
       </c>
       <c r="AE5" t="n">
-        <v>347701000</v>
+        <v>295705000</v>
       </c>
       <c r="AF5" t="n">
-        <v>135729000</v>
+        <v>-1599000</v>
       </c>
       <c r="AG5" t="n">
-        <v>781000</v>
+        <v>-46136000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-4291000</v>
+        <v>1907000</v>
       </c>
       <c r="AI5" t="n">
-        <v>3510000</v>
+        <v>44229000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-156533000</v>
+        <v>-33353000</v>
       </c>
       <c r="AK5" t="n">
-        <v>183108000</v>
+        <v>53892000</v>
       </c>
       <c r="AL5" t="n">
-        <v>26575000</v>
+        <v>20539000</v>
       </c>
       <c r="AM5" t="n">
-        <v>269834000</v>
+        <v>269589000</v>
       </c>
       <c r="AN5" t="n">
-        <v>381147000</v>
+        <v>417810000</v>
       </c>
       <c r="AO5" t="n">
-        <v>92382000</v>
+        <v>87986000</v>
       </c>
       <c r="AP5" t="n">
-        <v>320285000</v>
+        <v>364122000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>93974000</v>
+        <v>112233000</v>
       </c>
       <c r="AR5" t="n">
-        <v>226311000</v>
+        <v>251889000</v>
       </c>
       <c r="AS5" t="n">
-        <v>650981000</v>
+        <v>687399000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1453102000</v>
+        <v>1299252000</v>
       </c>
       <c r="AU5" t="n">
-        <v>2104083000</v>
+        <v>1986651000</v>
       </c>
       <c r="AV5" t="n">
-        <v>2104083000</v>
+        <v>1986651000</v>
       </c>
     </row>
   </sheetData>
@@ -1662,948 +1662,948 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>19600000</v>
       </c>
       <c r="C2" t="n">
-        <v>2113161805</v>
+        <v>1915436805</v>
       </c>
       <c r="D2" t="n">
-        <v>2132761805</v>
+        <v>1935036805</v>
       </c>
       <c r="E2" t="n">
-        <v>313730000</v>
+        <v>1820284000</v>
       </c>
       <c r="F2" t="n">
-        <v>1284051000</v>
+        <v>2654697000</v>
       </c>
       <c r="G2" t="n">
-        <v>1279909000</v>
+        <v>1225493000</v>
       </c>
       <c r="H2" t="n">
-        <v>5057688000</v>
+        <v>6534587000</v>
       </c>
       <c r="I2" t="n">
-        <v>749943000</v>
+        <v>1057182000</v>
       </c>
       <c r="J2" t="n">
-        <v>1279909000</v>
+        <v>1225493000</v>
       </c>
       <c r="K2" t="n">
-        <v>28740000</v>
+        <v>33466000</v>
       </c>
       <c r="L2" t="n">
-        <v>3802377000</v>
+        <v>3913356000</v>
       </c>
       <c r="M2" t="n">
-        <v>4508298000</v>
+        <v>6301535000</v>
       </c>
       <c r="N2" t="n">
-        <v>3816221000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>13844000</v>
-      </c>
+        <v>3913356000</v>
+      </c>
+      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
-        <v>3802377000</v>
+        <v>3913356000</v>
       </c>
       <c r="Q2" t="n">
-        <v>109940000</v>
+        <v>532177000</v>
       </c>
       <c r="R2" t="n">
-        <v>157670000</v>
+        <v>134651000</v>
       </c>
       <c r="S2" t="n">
-        <v>-286315000</v>
+        <v>273524000</v>
       </c>
       <c r="T2" t="n">
-        <v>3874168000</v>
+        <v>3636950000</v>
       </c>
       <c r="U2" t="n">
-        <v>367000</v>
+        <v>326000</v>
       </c>
       <c r="V2" t="n">
-        <v>367000</v>
+        <v>326000</v>
       </c>
       <c r="W2" t="n">
-        <v>3234373000</v>
+        <v>4131402000</v>
       </c>
       <c r="X2" t="n">
-        <v>2107718000</v>
-      </c>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+        <v>3204799000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>542041000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>53805000</v>
+      </c>
       <c r="AA2" t="n">
-        <v>6342000</v>
+        <v>645000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1262967000</v>
+        <v>541396000</v>
       </c>
       <c r="AC2" t="n">
-        <v>32995000</v>
+        <v>75269000</v>
       </c>
       <c r="AD2" t="n">
-        <v>73847000</v>
+        <v>117731000</v>
       </c>
       <c r="AE2" t="n">
-        <v>731567000</v>
+        <v>2415953000</v>
       </c>
       <c r="AF2" t="n">
-        <v>25646000</v>
+        <v>27774000</v>
       </c>
       <c r="AG2" t="n">
-        <v>705921000</v>
+        <v>2388179000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1126655000</v>
+        <v>926603000</v>
       </c>
       <c r="AI2" t="n">
-        <v>552484000</v>
+        <v>238744000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3094000</v>
+        <v>5692000</v>
       </c>
       <c r="AK2" t="n">
-        <v>549390000</v>
+        <v>233052000</v>
       </c>
       <c r="AL2" t="n">
-        <v>523135000</v>
+        <v>637854000</v>
       </c>
       <c r="AM2" t="n">
-        <v>176514000</v>
+        <v>298212000</v>
       </c>
       <c r="AN2" t="n">
-        <v>37266000</v>
+        <v>58589000</v>
       </c>
       <c r="AO2" t="n">
-        <v>309355000</v>
+        <v>281053000</v>
       </c>
       <c r="AP2" t="n">
-        <v>7050594000</v>
+        <v>8044758000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5173996000</v>
+        <v>6060973000</v>
       </c>
       <c r="AR2" t="n">
-        <v>2895000</v>
+        <v>524000</v>
       </c>
       <c r="AS2" t="n">
-        <v>21801000</v>
+        <v>7630000</v>
       </c>
       <c r="AT2" t="n">
-        <v>941741000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>500000</v>
-      </c>
+        <v>1246730000</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>941241000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>46808000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>46808000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
+        <v>1246730000</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="n">
-        <v>2522468000</v>
+        <v>2687863000</v>
       </c>
       <c r="BA2" t="n">
-        <v>366049000</v>
+        <v>531444000</v>
       </c>
       <c r="BB2" t="n">
         <v>2156419000</v>
       </c>
       <c r="BC2" t="n">
-        <v>1606609000</v>
+        <v>1794414000</v>
       </c>
       <c r="BD2" t="n">
-        <v>-548247000</v>
+        <v>-154912000</v>
       </c>
       <c r="BE2" t="n">
-        <v>2154856000</v>
+        <v>1949326000</v>
       </c>
       <c r="BF2" t="n">
-        <v>118830000</v>
-      </c>
-      <c r="BG2" t="inlineStr"/>
+        <v>612538000</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>1723901000</v>
+      </c>
       <c r="BH2" t="n">
-        <v>942198000</v>
+        <v>552492000</v>
       </c>
       <c r="BI2" t="n">
-        <v>827437000</v>
+        <v>363730000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>266391000</v>
+        <v>420566000</v>
       </c>
       <c r="BK2" t="n">
         <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1876598000</v>
-      </c>
-      <c r="BM2" t="inlineStr"/>
-      <c r="BN2" t="n">
-        <v>121929000</v>
-      </c>
+        <v>1983785000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>2805000</v>
+      </c>
+      <c r="BN2" t="inlineStr"/>
       <c r="BO2" t="n">
-        <v>12605000</v>
+        <v>13995000</v>
       </c>
       <c r="BP2" t="n">
-        <v>27689000</v>
+        <v>374968000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>18394000</v>
+        <v>27449000</v>
       </c>
       <c r="BR2" t="n">
-        <v>272700000</v>
+        <v>231721000</v>
       </c>
       <c r="BS2" t="n">
-        <v>55822000</v>
+        <v>57006000</v>
       </c>
       <c r="BT2" t="n">
-        <v>157616000</v>
+        <v>115072000</v>
       </c>
       <c r="BU2" t="n">
-        <v>59262000</v>
+        <v>59643000</v>
       </c>
       <c r="BV2" t="n">
-        <v>18037000</v>
+        <v>52878000</v>
       </c>
       <c r="BW2" t="n">
-        <v>44714000</v>
+        <v>56012000</v>
       </c>
       <c r="BX2" t="n">
-        <v>418949000</v>
+        <v>423010000</v>
       </c>
       <c r="BY2" t="n">
-        <v>-24831000</v>
+        <v>-9452000</v>
       </c>
       <c r="BZ2" t="n">
-        <v>443780000</v>
+        <v>432462000</v>
       </c>
       <c r="CA2" t="n">
-        <v>941581000</v>
+        <v>800947000</v>
       </c>
       <c r="CB2" t="n">
-        <v>941581000</v>
+        <v>800947000</v>
       </c>
       <c r="CC2" t="n">
-        <v>941581000</v>
+        <v>800947000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>19600000</v>
       </c>
       <c r="C3" t="n">
-        <v>2141766305</v>
+        <v>1915436805</v>
       </c>
       <c r="D3" t="n">
-        <v>2161366305</v>
+        <v>1935036805</v>
       </c>
       <c r="E3" t="n">
-        <v>835202000</v>
+        <v>2116300000</v>
       </c>
       <c r="F3" t="n">
-        <v>1903217000</v>
+        <v>2822940000</v>
       </c>
       <c r="G3" t="n">
-        <v>1110824000</v>
+        <v>972234000</v>
       </c>
       <c r="H3" t="n">
-        <v>5559436000</v>
+        <v>6399583000</v>
       </c>
       <c r="I3" t="n">
-        <v>496740000</v>
+        <v>-733750000</v>
       </c>
       <c r="J3" t="n">
-        <v>1110824000</v>
+        <v>972234000</v>
       </c>
       <c r="K3" t="n">
-        <v>31693000</v>
+        <v>28071000</v>
       </c>
       <c r="L3" t="n">
-        <v>3687912000</v>
+        <v>3604714000</v>
       </c>
       <c r="M3" t="n">
-        <v>4609924000</v>
+        <v>4485673000</v>
       </c>
       <c r="N3" t="n">
-        <v>3687912000</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
+        <v>3604714000</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>3687912000</v>
+        <v>3604714000</v>
       </c>
       <c r="Q3" t="n">
-        <v>107270000</v>
+        <v>514461000</v>
       </c>
       <c r="R3" t="n">
         <v>134651000</v>
       </c>
       <c r="S3" t="n">
-        <v>-418521000</v>
+        <v>-273779000</v>
       </c>
       <c r="T3" t="n">
-        <v>3874168000</v>
+        <v>3636950000</v>
       </c>
       <c r="U3" t="n">
-        <v>367000</v>
+        <v>326000</v>
       </c>
       <c r="V3" t="n">
-        <v>367000</v>
+        <v>326000</v>
       </c>
       <c r="W3" t="n">
-        <v>3762000000</v>
+        <v>4316141000</v>
       </c>
       <c r="X3" t="n">
-        <v>2227822000</v>
-      </c>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
+        <v>1643584000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>571500000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
       <c r="AA3" t="n">
-        <v>6332000</v>
+        <v>4388000</v>
       </c>
       <c r="AB3" t="n">
-        <v>1146499000</v>
+        <v>567112000</v>
       </c>
       <c r="AC3" t="n">
-        <v>55023000</v>
+        <v>73123000</v>
       </c>
       <c r="AD3" t="n">
-        <v>69192000</v>
+        <v>92201000</v>
       </c>
       <c r="AE3" t="n">
-        <v>950776000</v>
+        <v>906760000</v>
       </c>
       <c r="AF3" t="n">
-        <v>28764000</v>
+        <v>25801000</v>
       </c>
       <c r="AG3" t="n">
-        <v>922012000</v>
+        <v>880959000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1534178000</v>
+        <v>2672557000</v>
       </c>
       <c r="AI3" t="n">
-        <v>952441000</v>
+        <v>1916180000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2929000</v>
+        <v>2270000</v>
       </c>
       <c r="AK3" t="n">
-        <v>949512000</v>
+        <v>1913910000</v>
       </c>
       <c r="AL3" t="n">
-        <v>544509000</v>
+        <v>694329000</v>
       </c>
       <c r="AM3" t="n">
-        <v>259121000</v>
+        <v>312204000</v>
       </c>
       <c r="AN3" t="n">
-        <v>39632000</v>
+        <v>55995000</v>
       </c>
       <c r="AO3" t="n">
-        <v>245756000</v>
+        <v>326130000</v>
       </c>
       <c r="AP3" t="n">
-        <v>7449912000</v>
+        <v>7920855000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5418994000</v>
+        <v>5982048000</v>
       </c>
       <c r="AR3" t="n">
-        <v>850000</v>
+        <v>565000</v>
       </c>
       <c r="AS3" t="n">
-        <v>21186000</v>
+        <v>18178000</v>
       </c>
       <c r="AT3" t="n">
-        <v>995781000</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>500000</v>
-      </c>
+        <v>1046616000</v>
+      </c>
+      <c r="AU3" t="inlineStr"/>
       <c r="AV3" t="n">
-        <v>995281000</v>
+        <v>1046616000</v>
       </c>
       <c r="AW3" t="n">
-        <v>42403000</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>42403000</v>
+        <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>115500000</v>
+        <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2577088000</v>
+        <v>2632480000</v>
       </c>
       <c r="BA3" t="n">
-        <v>420669000</v>
+        <v>476061000</v>
       </c>
       <c r="BB3" t="n">
         <v>2156419000</v>
       </c>
       <c r="BC3" t="n">
-        <v>1660938000</v>
+        <v>1964417000</v>
       </c>
       <c r="BD3" t="n">
-        <v>-377855000</v>
+        <v>-251154000</v>
       </c>
       <c r="BE3" t="n">
-        <v>2038793000</v>
+        <v>2215571000</v>
       </c>
       <c r="BF3" t="n">
-        <v>344885000</v>
-      </c>
-      <c r="BG3" t="inlineStr"/>
+        <v>496920000</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1937380000</v>
+      </c>
       <c r="BH3" t="n">
-        <v>805360000</v>
+        <v>703127000</v>
       </c>
       <c r="BI3" t="n">
-        <v>614724000</v>
+        <v>606393000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>273824000</v>
+        <v>409131000</v>
       </c>
       <c r="BK3" t="n">
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>2030918000</v>
-      </c>
-      <c r="BM3" t="inlineStr"/>
-      <c r="BN3" t="n">
+        <v>1938807000</v>
+      </c>
+      <c r="BM3" t="n">
         <v>0</v>
       </c>
+      <c r="BN3" t="inlineStr"/>
       <c r="BO3" t="n">
-        <v>8719000</v>
+        <v>8447000</v>
       </c>
       <c r="BP3" t="n">
-        <v>161695000</v>
+        <v>394458000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>20944000</v>
+        <v>25920000</v>
       </c>
       <c r="BR3" t="n">
-        <v>259707000</v>
+        <v>326031000</v>
       </c>
       <c r="BS3" t="n">
-        <v>92266000</v>
+        <v>96557000</v>
       </c>
       <c r="BT3" t="n">
-        <v>120434000</v>
+        <v>148389000</v>
       </c>
       <c r="BU3" t="n">
-        <v>47007000</v>
+        <v>81085000</v>
       </c>
       <c r="BV3" t="n">
-        <v>107057000</v>
+        <v>35383000</v>
       </c>
       <c r="BW3" t="n">
-        <v>41925000</v>
+        <v>37513000</v>
       </c>
       <c r="BX3" t="n">
-        <v>394549000</v>
+        <v>432486000</v>
       </c>
       <c r="BY3" t="n">
-        <v>-20813000</v>
+        <v>-15124000</v>
       </c>
       <c r="BZ3" t="n">
-        <v>415362000</v>
+        <v>447610000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1036322000</v>
+        <v>678569000</v>
       </c>
       <c r="CB3" t="n">
-        <v>1036322000</v>
+        <v>678569000</v>
       </c>
       <c r="CC3" t="n">
-        <v>1036322000</v>
+        <v>678569000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>19600000</v>
       </c>
       <c r="C4" t="n">
-        <v>1915436805</v>
+        <v>2141766305</v>
       </c>
       <c r="D4" t="n">
-        <v>1935036805</v>
+        <v>2161366305</v>
       </c>
       <c r="E4" t="n">
-        <v>2116300000</v>
+        <v>835202000</v>
       </c>
       <c r="F4" t="n">
-        <v>2822940000</v>
+        <v>1903217000</v>
       </c>
       <c r="G4" t="n">
-        <v>972234000</v>
+        <v>1110824000</v>
       </c>
       <c r="H4" t="n">
-        <v>6399583000</v>
+        <v>5559436000</v>
       </c>
       <c r="I4" t="n">
-        <v>-733750000</v>
+        <v>496740000</v>
       </c>
       <c r="J4" t="n">
-        <v>972234000</v>
+        <v>1110824000</v>
       </c>
       <c r="K4" t="n">
-        <v>28071000</v>
+        <v>31693000</v>
       </c>
       <c r="L4" t="n">
-        <v>3604714000</v>
+        <v>3687912000</v>
       </c>
       <c r="M4" t="n">
-        <v>4485673000</v>
+        <v>4609924000</v>
       </c>
       <c r="N4" t="n">
-        <v>3604714000</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>3687912000</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
       <c r="P4" t="n">
-        <v>3604714000</v>
+        <v>3687912000</v>
       </c>
       <c r="Q4" t="n">
-        <v>514461000</v>
+        <v>107270000</v>
       </c>
       <c r="R4" t="n">
         <v>134651000</v>
       </c>
       <c r="S4" t="n">
-        <v>-273779000</v>
+        <v>-418521000</v>
       </c>
       <c r="T4" t="n">
-        <v>3636950000</v>
+        <v>3874168000</v>
       </c>
       <c r="U4" t="n">
-        <v>326000</v>
+        <v>367000</v>
       </c>
       <c r="V4" t="n">
-        <v>326000</v>
+        <v>367000</v>
       </c>
       <c r="W4" t="n">
-        <v>4316141000</v>
+        <v>3762000000</v>
       </c>
       <c r="X4" t="n">
-        <v>1643584000</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>571500000</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
+        <v>2227822000</v>
+      </c>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>4388000</v>
+        <v>6332000</v>
       </c>
       <c r="AB4" t="n">
-        <v>567112000</v>
+        <v>1146499000</v>
       </c>
       <c r="AC4" t="n">
-        <v>73123000</v>
+        <v>55023000</v>
       </c>
       <c r="AD4" t="n">
-        <v>92201000</v>
+        <v>69192000</v>
       </c>
       <c r="AE4" t="n">
-        <v>906760000</v>
+        <v>950776000</v>
       </c>
       <c r="AF4" t="n">
-        <v>25801000</v>
+        <v>28764000</v>
       </c>
       <c r="AG4" t="n">
-        <v>880959000</v>
+        <v>922012000</v>
       </c>
       <c r="AH4" t="n">
-        <v>2672557000</v>
+        <v>1534178000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1916180000</v>
+        <v>952441000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>2270000</v>
+        <v>2929000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1913910000</v>
+        <v>949512000</v>
       </c>
       <c r="AL4" t="n">
-        <v>694329000</v>
+        <v>544509000</v>
       </c>
       <c r="AM4" t="n">
-        <v>312204000</v>
+        <v>259121000</v>
       </c>
       <c r="AN4" t="n">
-        <v>55995000</v>
+        <v>39632000</v>
       </c>
       <c r="AO4" t="n">
-        <v>326130000</v>
+        <v>245756000</v>
       </c>
       <c r="AP4" t="n">
-        <v>7920855000</v>
+        <v>7449912000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5982048000</v>
+        <v>5418994000</v>
       </c>
       <c r="AR4" t="n">
-        <v>565000</v>
+        <v>850000</v>
       </c>
       <c r="AS4" t="n">
-        <v>18178000</v>
+        <v>21186000</v>
       </c>
       <c r="AT4" t="n">
-        <v>1046616000</v>
-      </c>
-      <c r="AU4" t="inlineStr"/>
+        <v>995781000</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>500000</v>
+      </c>
       <c r="AV4" t="n">
-        <v>1046616000</v>
+        <v>995281000</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>42403000</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>42403000</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>115500000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2632480000</v>
+        <v>2577088000</v>
       </c>
       <c r="BA4" t="n">
-        <v>476061000</v>
+        <v>420669000</v>
       </c>
       <c r="BB4" t="n">
         <v>2156419000</v>
       </c>
       <c r="BC4" t="n">
-        <v>1964417000</v>
+        <v>1660938000</v>
       </c>
       <c r="BD4" t="n">
-        <v>-251154000</v>
+        <v>-377855000</v>
       </c>
       <c r="BE4" t="n">
-        <v>2215571000</v>
+        <v>2038793000</v>
       </c>
       <c r="BF4" t="n">
-        <v>496920000</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>1937380000</v>
-      </c>
+        <v>344885000</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>703127000</v>
+        <v>805360000</v>
       </c>
       <c r="BI4" t="n">
-        <v>606393000</v>
+        <v>614724000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>409131000</v>
+        <v>273824000</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1938807000</v>
-      </c>
-      <c r="BM4" t="n">
+        <v>2030918000</v>
+      </c>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="n">
         <v>0</v>
       </c>
-      <c r="BN4" t="inlineStr"/>
       <c r="BO4" t="n">
-        <v>8447000</v>
+        <v>8719000</v>
       </c>
       <c r="BP4" t="n">
-        <v>394458000</v>
+        <v>161695000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>25920000</v>
+        <v>20944000</v>
       </c>
       <c r="BR4" t="n">
-        <v>326031000</v>
+        <v>259707000</v>
       </c>
       <c r="BS4" t="n">
-        <v>96557000</v>
+        <v>92266000</v>
       </c>
       <c r="BT4" t="n">
-        <v>148389000</v>
+        <v>120434000</v>
       </c>
       <c r="BU4" t="n">
-        <v>81085000</v>
+        <v>47007000</v>
       </c>
       <c r="BV4" t="n">
-        <v>35383000</v>
+        <v>107057000</v>
       </c>
       <c r="BW4" t="n">
-        <v>37513000</v>
+        <v>41925000</v>
       </c>
       <c r="BX4" t="n">
-        <v>432486000</v>
+        <v>394549000</v>
       </c>
       <c r="BY4" t="n">
-        <v>-15124000</v>
+        <v>-20813000</v>
       </c>
       <c r="BZ4" t="n">
-        <v>447610000</v>
+        <v>415362000</v>
       </c>
       <c r="CA4" t="n">
-        <v>678569000</v>
+        <v>1036322000</v>
       </c>
       <c r="CB4" t="n">
-        <v>678569000</v>
+        <v>1036322000</v>
       </c>
       <c r="CC4" t="n">
-        <v>678569000</v>
+        <v>1036322000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>19600000</v>
       </c>
       <c r="C5" t="n">
-        <v>1915436805</v>
+        <v>2113161805</v>
       </c>
       <c r="D5" t="n">
-        <v>1935036805</v>
+        <v>2132761805</v>
       </c>
       <c r="E5" t="n">
-        <v>1820284000</v>
+        <v>313730000</v>
       </c>
       <c r="F5" t="n">
-        <v>2654697000</v>
+        <v>1284051000</v>
       </c>
       <c r="G5" t="n">
-        <v>1225493000</v>
+        <v>1279909000</v>
       </c>
       <c r="H5" t="n">
-        <v>6534587000</v>
+        <v>5057688000</v>
       </c>
       <c r="I5" t="n">
-        <v>1057182000</v>
+        <v>749943000</v>
       </c>
       <c r="J5" t="n">
-        <v>1225493000</v>
+        <v>1279909000</v>
       </c>
       <c r="K5" t="n">
-        <v>33466000</v>
+        <v>28740000</v>
       </c>
       <c r="L5" t="n">
-        <v>3913356000</v>
+        <v>3802377000</v>
       </c>
       <c r="M5" t="n">
-        <v>6301535000</v>
+        <v>4508298000</v>
       </c>
       <c r="N5" t="n">
-        <v>3913356000</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>3816221000</v>
+      </c>
+      <c r="O5" t="n">
+        <v>13844000</v>
+      </c>
       <c r="P5" t="n">
-        <v>3913356000</v>
+        <v>3802377000</v>
       </c>
       <c r="Q5" t="n">
-        <v>532177000</v>
+        <v>109940000</v>
       </c>
       <c r="R5" t="n">
-        <v>134651000</v>
+        <v>157670000</v>
       </c>
       <c r="S5" t="n">
-        <v>273524000</v>
+        <v>-286315000</v>
       </c>
       <c r="T5" t="n">
-        <v>3636950000</v>
+        <v>3874168000</v>
       </c>
       <c r="U5" t="n">
-        <v>326000</v>
+        <v>367000</v>
       </c>
       <c r="V5" t="n">
-        <v>326000</v>
+        <v>367000</v>
       </c>
       <c r="W5" t="n">
-        <v>4131402000</v>
+        <v>3234373000</v>
       </c>
       <c r="X5" t="n">
-        <v>3204799000</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>542041000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>53805000</v>
-      </c>
+        <v>2107718000</v>
+      </c>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>645000</v>
+        <v>6342000</v>
       </c>
       <c r="AB5" t="n">
-        <v>541396000</v>
+        <v>1262967000</v>
       </c>
       <c r="AC5" t="n">
-        <v>75269000</v>
+        <v>32995000</v>
       </c>
       <c r="AD5" t="n">
-        <v>117731000</v>
+        <v>73847000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2415953000</v>
+        <v>731567000</v>
       </c>
       <c r="AF5" t="n">
-        <v>27774000</v>
+        <v>25646000</v>
       </c>
       <c r="AG5" t="n">
-        <v>2388179000</v>
+        <v>705921000</v>
       </c>
       <c r="AH5" t="n">
-        <v>926603000</v>
+        <v>1126655000</v>
       </c>
       <c r="AI5" t="n">
-        <v>238744000</v>
+        <v>552484000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5692000</v>
+        <v>3094000</v>
       </c>
       <c r="AK5" t="n">
-        <v>233052000</v>
+        <v>549390000</v>
       </c>
       <c r="AL5" t="n">
-        <v>637854000</v>
+        <v>523135000</v>
       </c>
       <c r="AM5" t="n">
-        <v>298212000</v>
+        <v>176514000</v>
       </c>
       <c r="AN5" t="n">
-        <v>58589000</v>
+        <v>37266000</v>
       </c>
       <c r="AO5" t="n">
-        <v>281053000</v>
+        <v>309355000</v>
       </c>
       <c r="AP5" t="n">
-        <v>8044758000</v>
+        <v>7050594000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>6060973000</v>
+        <v>5173996000</v>
       </c>
       <c r="AR5" t="n">
-        <v>524000</v>
+        <v>2895000</v>
       </c>
       <c r="AS5" t="n">
-        <v>7630000</v>
+        <v>21801000</v>
       </c>
       <c r="AT5" t="n">
-        <v>1246730000</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
+        <v>941741000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>500000</v>
+      </c>
       <c r="AV5" t="n">
-        <v>1246730000</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
+        <v>941241000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>46808000</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>46808000</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ5" t="n">
-        <v>2687863000</v>
+        <v>2522468000</v>
       </c>
       <c r="BA5" t="n">
-        <v>531444000</v>
+        <v>366049000</v>
       </c>
       <c r="BB5" t="n">
         <v>2156419000</v>
       </c>
       <c r="BC5" t="n">
-        <v>1794414000</v>
+        <v>1606609000</v>
       </c>
       <c r="BD5" t="n">
-        <v>-154912000</v>
+        <v>-548247000</v>
       </c>
       <c r="BE5" t="n">
-        <v>1949326000</v>
+        <v>2154856000</v>
       </c>
       <c r="BF5" t="n">
-        <v>612538000</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>1723901000</v>
-      </c>
+        <v>118830000</v>
+      </c>
+      <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="n">
-        <v>552492000</v>
+        <v>942198000</v>
       </c>
       <c r="BI5" t="n">
-        <v>363730000</v>
+        <v>827437000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>420566000</v>
+        <v>266391000</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1983785000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>2805000</v>
-      </c>
-      <c r="BN5" t="inlineStr"/>
+        <v>1876598000</v>
+      </c>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="n">
+        <v>121929000</v>
+      </c>
       <c r="BO5" t="n">
-        <v>13995000</v>
+        <v>12605000</v>
       </c>
       <c r="BP5" t="n">
-        <v>374968000</v>
+        <v>27689000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>27449000</v>
+        <v>18394000</v>
       </c>
       <c r="BR5" t="n">
-        <v>231721000</v>
+        <v>272700000</v>
       </c>
       <c r="BS5" t="n">
-        <v>57006000</v>
+        <v>55822000</v>
       </c>
       <c r="BT5" t="n">
-        <v>115072000</v>
+        <v>157616000</v>
       </c>
       <c r="BU5" t="n">
-        <v>59643000</v>
+        <v>59262000</v>
       </c>
       <c r="BV5" t="n">
-        <v>52878000</v>
+        <v>18037000</v>
       </c>
       <c r="BW5" t="n">
-        <v>56012000</v>
+        <v>44714000</v>
       </c>
       <c r="BX5" t="n">
-        <v>423010000</v>
+        <v>418949000</v>
       </c>
       <c r="BY5" t="n">
-        <v>-9452000</v>
+        <v>-24831000</v>
       </c>
       <c r="BZ5" t="n">
-        <v>432462000</v>
+        <v>443780000</v>
       </c>
       <c r="CA5" t="n">
-        <v>800947000</v>
+        <v>941581000</v>
       </c>
       <c r="CB5" t="n">
-        <v>800947000</v>
+        <v>941581000</v>
       </c>
       <c r="CC5" t="n">
-        <v>800947000</v>
+        <v>941581000</v>
       </c>
     </row>
   </sheetData>
@@ -2894,654 +2894,654 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>182319000</v>
+        <v>-488494000</v>
       </c>
       <c r="C2" t="n">
-        <v>-23019000</v>
+        <v>-146194000</v>
       </c>
       <c r="D2" t="n">
-        <v>-1735773000</v>
+        <v>-975554000</v>
       </c>
       <c r="E2" t="n">
-        <v>1119560000</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>565030000</v>
+      </c>
+      <c r="F2" t="n">
+        <v>18227000</v>
+      </c>
       <c r="G2" t="n">
-        <v>-191671000</v>
+        <v>-566324000</v>
       </c>
       <c r="H2" t="n">
-        <v>941710000</v>
+        <v>800947000</v>
       </c>
       <c r="I2" t="n">
-        <v>1036322000</v>
+        <v>2308452000</v>
       </c>
       <c r="J2" t="n">
-        <v>3263000</v>
+        <v>-63341000</v>
       </c>
       <c r="K2" t="n">
-        <v>-97875000</v>
+        <v>-1444164000</v>
       </c>
       <c r="L2" t="n">
-        <v>-657764000</v>
+        <v>-653159000</v>
       </c>
       <c r="M2" t="n">
-        <v>39526000</v>
+        <v>95000</v>
       </c>
       <c r="N2" t="n">
-        <v>-53759000</v>
-      </c>
-      <c r="O2" t="inlineStr"/>
+        <v>-71275000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-16270000</v>
+      </c>
       <c r="P2" t="n">
-        <v>-23019000</v>
+        <v>-127967000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-23019000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>-146194000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>18227000</v>
+      </c>
       <c r="S2" t="n">
-        <v>-616213000</v>
+        <v>-410524000</v>
       </c>
       <c r="T2" t="n">
-        <v>-616213000</v>
+        <v>-410524000</v>
       </c>
       <c r="U2" t="n">
-        <v>-1735773000</v>
+        <v>-975554000</v>
       </c>
       <c r="V2" t="n">
-        <v>1119560000</v>
+        <v>565030000</v>
       </c>
       <c r="W2" t="n">
-        <v>185899000</v>
+        <v>-868835000</v>
       </c>
       <c r="X2" t="n">
-        <v>234108000</v>
+        <v>16964000</v>
       </c>
       <c r="Y2" t="n">
-        <v>19637000</v>
+        <v>12035000</v>
       </c>
       <c r="Z2" t="n">
-        <v>148987000</v>
+        <v>-122216000</v>
       </c>
       <c r="AA2" t="n">
-        <v>169134000</v>
+        <v>1982012000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-20147000</v>
+        <v>-2104228000</v>
       </c>
       <c r="AC2" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>15000000</v>
-      </c>
+        <v>-210871000</v>
+      </c>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="n">
-        <v>-4500000</v>
+        <v>-210871000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-997000</v>
+        <v>-1145000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-997000</v>
+        <v>-1145000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-190120000</v>
+        <v>-563602000</v>
       </c>
       <c r="AI2" t="n">
-        <v>554000</v>
+        <v>1577000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-190674000</v>
+        <v>-565179000</v>
       </c>
       <c r="AK2" t="n">
-        <v>373990000</v>
+        <v>77830000</v>
       </c>
       <c r="AL2" t="n">
-        <v>-79127000</v>
+        <v>-45145000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-32943000</v>
+        <v>-261518000</v>
       </c>
       <c r="AN2" t="n">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-15600000</v>
+        <v>7698000</v>
       </c>
       <c r="AP2" t="n">
-        <v>28489000</v>
+        <v>-72367000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-2439000</v>
+        <v>-22982000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-17482000</v>
+        <v>-69073000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-25921000</v>
+        <v>-104805000</v>
       </c>
       <c r="AT2" t="n">
-        <v>13565000</v>
+        <v>73616000</v>
       </c>
       <c r="AU2" t="n">
-        <v>4192000</v>
+        <v>20584000</v>
       </c>
       <c r="AV2" t="n">
-        <v>213861000</v>
+        <v>153154000</v>
       </c>
       <c r="AW2" t="n">
-        <v>55617000</v>
+        <v>52363000</v>
       </c>
       <c r="AX2" t="n">
-        <v>158244000</v>
+        <v>100791000</v>
       </c>
       <c r="AY2" t="n">
-        <v>-91120000</v>
+        <v>-210066000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3626000</v>
+        <v>641000</v>
       </c>
       <c r="BA2" t="n">
-        <v>1907000</v>
+        <v>4839000</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-9486000</v>
       </c>
       <c r="BC2" t="n">
-        <v>295705000</v>
+        <v>347701000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>195569000</v>
+        <v>136509000</v>
       </c>
       <c r="C3" t="n">
-        <v>-10274000</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-2870553000</v>
+        <v>-740911000</v>
       </c>
       <c r="E3" t="n">
-        <v>2045204000</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>673041000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
       <c r="G3" t="n">
-        <v>-187836000</v>
+        <v>-249542000</v>
       </c>
       <c r="H3" t="n">
-        <v>1036322000</v>
+        <v>678569000</v>
       </c>
       <c r="I3" t="n">
-        <v>678569000</v>
+        <v>800947000</v>
       </c>
       <c r="J3" t="n">
-        <v>-35324000</v>
+        <v>7571000</v>
       </c>
       <c r="K3" t="n">
-        <v>393077000</v>
+        <v>-129949000</v>
       </c>
       <c r="L3" t="n">
-        <v>-429502000</v>
+        <v>-143196000</v>
       </c>
       <c r="M3" t="n">
-        <v>501006000</v>
+        <v>2220000</v>
       </c>
       <c r="N3" t="n">
-        <v>-70691000</v>
+        <v>-72856000</v>
       </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
-        <v>-10274000</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-10274000</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
       <c r="S3" t="n">
-        <v>-825349000</v>
+        <v>-67870000</v>
       </c>
       <c r="T3" t="n">
-        <v>-825349000</v>
+        <v>-67870000</v>
       </c>
       <c r="U3" t="n">
-        <v>-2870553000</v>
+        <v>-740911000</v>
       </c>
       <c r="V3" t="n">
-        <v>2045204000</v>
+        <v>673041000</v>
       </c>
       <c r="W3" t="n">
-        <v>439174000</v>
+        <v>-372804000</v>
       </c>
       <c r="X3" t="n">
-        <v>513199000</v>
+        <v>16199000</v>
       </c>
       <c r="Y3" t="n">
-        <v>56373000</v>
+        <v>9437000</v>
       </c>
       <c r="Z3" t="n">
-        <v>52949000</v>
+        <v>-68356000</v>
       </c>
       <c r="AA3" t="n">
-        <v>117401000</v>
+        <v>164875000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-64452000</v>
+        <v>-233231000</v>
       </c>
       <c r="AC3" t="n">
-        <v>3841000</v>
+        <v>-81202000</v>
       </c>
       <c r="AD3" t="n">
-        <v>32341000</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-28500000</v>
+        <v>-81202000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-158000</v>
+        <v>-214000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-158000</v>
+        <v>-214000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-187030000</v>
+        <v>-248668000</v>
       </c>
       <c r="AI3" t="n">
-        <v>648000</v>
+        <v>660000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-187678000</v>
+        <v>-249328000</v>
       </c>
       <c r="AK3" t="n">
-        <v>383405000</v>
+        <v>386051000</v>
       </c>
       <c r="AL3" t="n">
-        <v>-80327000</v>
+        <v>-80507000</v>
       </c>
       <c r="AM3" t="n">
-        <v>31415000</v>
+        <v>-17905000</v>
       </c>
       <c r="AN3" t="n">
-        <v>1944000</v>
+        <v>3743000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-2585000</v>
+        <v>-31727000</v>
       </c>
       <c r="AP3" t="n">
-        <v>-46672000</v>
+        <v>88990000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-6396000</v>
+        <v>38731000</v>
       </c>
       <c r="AR3" t="n">
-        <v>57042000</v>
+        <v>-96444000</v>
       </c>
       <c r="AS3" t="n">
-        <v>28082000</v>
+        <v>-21198000</v>
       </c>
       <c r="AT3" t="n">
-        <v>169882000</v>
+        <v>142290000</v>
       </c>
       <c r="AU3" t="n">
-        <v>19007000</v>
+        <v>24817000</v>
       </c>
       <c r="AV3" t="n">
-        <v>211216000</v>
+        <v>185454000</v>
       </c>
       <c r="AW3" t="n">
-        <v>55550000</v>
+        <v>55597000</v>
       </c>
       <c r="AX3" t="n">
-        <v>155666000</v>
+        <v>129857000</v>
       </c>
       <c r="AY3" t="n">
-        <v>34163000</v>
+        <v>395067000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>34794000</v>
+        <v>178116000</v>
       </c>
       <c r="BA3" t="n">
-        <v>399000</v>
+        <v>1901000</v>
       </c>
       <c r="BB3" t="n">
-        <v>-683000</v>
+        <v>0</v>
       </c>
       <c r="BC3" t="n">
-        <v>-55953000</v>
+        <v>-459165000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>136509000</v>
+        <v>195569000</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-10274000</v>
       </c>
       <c r="D4" t="n">
-        <v>-740911000</v>
+        <v>-2870553000</v>
       </c>
       <c r="E4" t="n">
-        <v>673041000</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
+        <v>2045204000</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>-249542000</v>
+        <v>-187836000</v>
       </c>
       <c r="H4" t="n">
+        <v>1036322000</v>
+      </c>
+      <c r="I4" t="n">
         <v>678569000</v>
       </c>
-      <c r="I4" t="n">
-        <v>800947000</v>
-      </c>
       <c r="J4" t="n">
-        <v>7571000</v>
+        <v>-35324000</v>
       </c>
       <c r="K4" t="n">
-        <v>-129949000</v>
+        <v>393077000</v>
       </c>
       <c r="L4" t="n">
-        <v>-143196000</v>
+        <v>-429502000</v>
       </c>
       <c r="M4" t="n">
-        <v>2220000</v>
+        <v>501006000</v>
       </c>
       <c r="N4" t="n">
-        <v>-72856000</v>
+        <v>-70691000</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-10274000</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
+        <v>-10274000</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>-67870000</v>
+        <v>-825349000</v>
       </c>
       <c r="T4" t="n">
-        <v>-67870000</v>
+        <v>-825349000</v>
       </c>
       <c r="U4" t="n">
-        <v>-740911000</v>
+        <v>-2870553000</v>
       </c>
       <c r="V4" t="n">
-        <v>673041000</v>
+        <v>2045204000</v>
       </c>
       <c r="W4" t="n">
-        <v>-372804000</v>
+        <v>439174000</v>
       </c>
       <c r="X4" t="n">
-        <v>16199000</v>
+        <v>513199000</v>
       </c>
       <c r="Y4" t="n">
-        <v>9437000</v>
+        <v>56373000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-68356000</v>
+        <v>52949000</v>
       </c>
       <c r="AA4" t="n">
-        <v>164875000</v>
+        <v>117401000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-233231000</v>
+        <v>-64452000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-81202000</v>
+        <v>3841000</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>32341000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-81202000</v>
+        <v>-28500000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-214000</v>
+        <v>-158000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-214000</v>
+        <v>-158000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-248668000</v>
+        <v>-187030000</v>
       </c>
       <c r="AI4" t="n">
-        <v>660000</v>
+        <v>648000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-249328000</v>
+        <v>-187678000</v>
       </c>
       <c r="AK4" t="n">
-        <v>386051000</v>
+        <v>383405000</v>
       </c>
       <c r="AL4" t="n">
-        <v>-80507000</v>
+        <v>-80327000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-17905000</v>
+        <v>31415000</v>
       </c>
       <c r="AN4" t="n">
-        <v>3743000</v>
+        <v>1944000</v>
       </c>
       <c r="AO4" t="n">
-        <v>-31727000</v>
+        <v>-2585000</v>
       </c>
       <c r="AP4" t="n">
-        <v>88990000</v>
+        <v>-46672000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>38731000</v>
+        <v>-6396000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-96444000</v>
+        <v>57042000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-21198000</v>
+        <v>28082000</v>
       </c>
       <c r="AT4" t="n">
-        <v>142290000</v>
+        <v>169882000</v>
       </c>
       <c r="AU4" t="n">
-        <v>24817000</v>
+        <v>19007000</v>
       </c>
       <c r="AV4" t="n">
-        <v>185454000</v>
+        <v>211216000</v>
       </c>
       <c r="AW4" t="n">
-        <v>55597000</v>
+        <v>55550000</v>
       </c>
       <c r="AX4" t="n">
-        <v>129857000</v>
+        <v>155666000</v>
       </c>
       <c r="AY4" t="n">
-        <v>395067000</v>
+        <v>34163000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>178116000</v>
+        <v>34794000</v>
       </c>
       <c r="BA4" t="n">
-        <v>1901000</v>
+        <v>399000</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-683000</v>
       </c>
       <c r="BC4" t="n">
-        <v>-459165000</v>
+        <v>-55953000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-488494000</v>
+        <v>182319000</v>
       </c>
       <c r="C5" t="n">
-        <v>-146194000</v>
+        <v>-23019000</v>
       </c>
       <c r="D5" t="n">
-        <v>-975554000</v>
+        <v>-1735773000</v>
       </c>
       <c r="E5" t="n">
-        <v>565030000</v>
-      </c>
-      <c r="F5" t="n">
-        <v>18227000</v>
-      </c>
+        <v>1119560000</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>-566324000</v>
+        <v>-191671000</v>
       </c>
       <c r="H5" t="n">
-        <v>800947000</v>
+        <v>941710000</v>
       </c>
       <c r="I5" t="n">
-        <v>2308452000</v>
+        <v>1036322000</v>
       </c>
       <c r="J5" t="n">
-        <v>-63341000</v>
+        <v>3263000</v>
       </c>
       <c r="K5" t="n">
-        <v>-1444164000</v>
+        <v>-97875000</v>
       </c>
       <c r="L5" t="n">
-        <v>-653159000</v>
+        <v>-657764000</v>
       </c>
       <c r="M5" t="n">
-        <v>95000</v>
+        <v>39526000</v>
       </c>
       <c r="N5" t="n">
-        <v>-71275000</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-16270000</v>
-      </c>
+        <v>-53759000</v>
+      </c>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
-        <v>-127967000</v>
+        <v>-23019000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-146194000</v>
-      </c>
-      <c r="R5" t="n">
-        <v>18227000</v>
-      </c>
+        <v>-23019000</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-410524000</v>
+        <v>-616213000</v>
       </c>
       <c r="T5" t="n">
-        <v>-410524000</v>
+        <v>-616213000</v>
       </c>
       <c r="U5" t="n">
-        <v>-975554000</v>
+        <v>-1735773000</v>
       </c>
       <c r="V5" t="n">
-        <v>565030000</v>
+        <v>1119560000</v>
       </c>
       <c r="W5" t="n">
-        <v>-868835000</v>
+        <v>185899000</v>
       </c>
       <c r="X5" t="n">
-        <v>16964000</v>
+        <v>234108000</v>
       </c>
       <c r="Y5" t="n">
-        <v>12035000</v>
+        <v>19637000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-122216000</v>
+        <v>148987000</v>
       </c>
       <c r="AA5" t="n">
-        <v>1982012000</v>
+        <v>169134000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-2104228000</v>
+        <v>-20147000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-210871000</v>
-      </c>
-      <c r="AD5" t="inlineStr"/>
+        <v>10500000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>15000000</v>
+      </c>
       <c r="AE5" t="n">
-        <v>-210871000</v>
+        <v>-4500000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1145000</v>
+        <v>-997000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1145000</v>
+        <v>-997000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-563602000</v>
+        <v>-190120000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1577000</v>
+        <v>554000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-565179000</v>
+        <v>-190674000</v>
       </c>
       <c r="AK5" t="n">
-        <v>77830000</v>
+        <v>373990000</v>
       </c>
       <c r="AL5" t="n">
-        <v>-45145000</v>
+        <v>-79127000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-261518000</v>
+        <v>-32943000</v>
       </c>
       <c r="AN5" t="n">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="AO5" t="n">
-        <v>7698000</v>
+        <v>-15600000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-72367000</v>
+        <v>28489000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-22982000</v>
+        <v>-2439000</v>
       </c>
       <c r="AR5" t="n">
-        <v>-69073000</v>
+        <v>-17482000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-104805000</v>
+        <v>-25921000</v>
       </c>
       <c r="AT5" t="n">
-        <v>73616000</v>
+        <v>13565000</v>
       </c>
       <c r="AU5" t="n">
-        <v>20584000</v>
+        <v>4192000</v>
       </c>
       <c r="AV5" t="n">
-        <v>153154000</v>
+        <v>213861000</v>
       </c>
       <c r="AW5" t="n">
-        <v>52363000</v>
+        <v>55617000</v>
       </c>
       <c r="AX5" t="n">
-        <v>100791000</v>
+        <v>158244000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-210066000</v>
+        <v>-91120000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>641000</v>
+        <v>3626000</v>
       </c>
       <c r="BA5" t="n">
-        <v>4839000</v>
+        <v>1907000</v>
       </c>
       <c r="BB5" t="n">
-        <v>-9486000</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
-        <v>347701000</v>
+        <v>295705000</v>
       </c>
     </row>
   </sheetData>
@@ -4121,192 +4121,192 @@
       </c>
       <c r="DI1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
           <t>shortName</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EU1" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Dr. Chen Cheney  Mao Ph.D.', 'age': 62, 'title': 'Chairman &amp; CEO', 'yearBorn': 1963, 'fiscalYear': 2025, 'totalPay': 4589744, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ying  Wu M.B.A.', 'age': 61, 'title': 'Executive VP &amp; Executive Director', 'yearBorn': 1964, 'fiscalYear': 2025, 'totalPay': 1055340, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Delin  Ren Ph.D.', 'age': 64, 'title': 'Executive Director', 'yearBorn': 1961, 'fiscalYear': 2025, 'totalPay': 4217885, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wei  Xiong', 'age': 41, 'title': 'Chief Financial Officer', 'yearBorn': 1984, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Susan  Chen Ph.D.', 'title': 'Chief Technology Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Zhixiong  Ye Ph.D.', 'age': 64, 'title': 'Chief Scientific Officer', 'yearBorn': 1961, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Han  Dai Ph.D.', 'age': 44, 'title': 'Chief Innovation Officer &amp; Head of Viva BioInnovator', 'yearBorn': 1981, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jianhua  Cai Ph.D.', 'title': 'Senior Vice President of Via Biotech Shanghai', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Jianguo  Ma Ph.D.', 'title': 'Senior VP &amp; President of Shanghai Langhua Pharmaceutical', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xianyong  Bu Ph.D.', 'title': 'CBO &amp; EVP of Viva Biotech (Shanghai)', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Dr. Chen Cheney  Mao Ph.D.', 'age': 62, 'title': 'Chairman &amp; CEO', 'yearBorn': 1963, 'fiscalYear': 2025, 'totalPay': 4586087, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ying  Wu M.B.A.', 'age': 61, 'title': 'Executive VP &amp; Executive Director', 'yearBorn': 1964, 'fiscalYear': 2025, 'totalPay': 1054499, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Delin  Ren Ph.D.', 'age': 64, 'title': 'Executive Director', 'yearBorn': 1961, 'fiscalYear': 2025, 'totalPay': 4214524, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Wei  Xiong', 'age': 41, 'title': 'Chief Financial Officer', 'yearBorn': 1984, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Susan  Chen Ph.D.', 'title': 'Chief Technology Officer', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dr. Zhixiong  Ye Ph.D.', 'age': 64, 'title': 'Chief Scientific Officer', 'yearBorn': 1961, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Han  Dai Ph.D.', 'age': 44, 'title': 'Chief Innovation Officer &amp; Head of Viva BioInnovator', 'yearBorn': 1981, 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Jianhua  Cai Ph.D.', 'title': 'Senior Vice President of Via Biotech Shanghai', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Jianguo  Ma Ph.D.', 'title': 'Senior VP &amp; President of Shanghai Langhua Pharmaceutical', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Xianyong  Bu Ph.D.', 'title': 'CBO &amp; EVP of Viva Biotech (Shanghai)', 'fiscalYear': 2025, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="R2" t="n">
@@ -4414,28 +4414,28 @@
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.27</v>
+        <v>1.14</v>
       </c>
       <c r="AD2" t="n">
         <v>1623801600</v>
@@ -4444,43 +4444,43 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.516</v>
+        <v>1.357</v>
       </c>
       <c r="AG2" t="n">
-        <v>17.714285</v>
+        <v>15.714286</v>
       </c>
       <c r="AH2" t="n">
-        <v>5.6363635</v>
+        <v>5</v>
       </c>
       <c r="AI2" t="n">
-        <v>648500</v>
+        <v>4199000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>648500</v>
+        <v>4199000</v>
       </c>
       <c r="AK2" t="n">
-        <v>6502105</v>
+        <v>5444956</v>
       </c>
       <c r="AL2" t="n">
-        <v>4827330</v>
+        <v>5285762</v>
       </c>
       <c r="AM2" t="n">
-        <v>4827330</v>
+        <v>5285762</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="AO2" t="n">
-        <v>1.25</v>
+        <v>1.09</v>
       </c>
       <c r="AP2" t="n">
-        <v>2593037568</v>
+        <v>2289435904</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2677734211</v>
+        <v>2353231048</v>
       </c>
       <c r="AR2" t="n">
-        <v>1.22</v>
+        <v>1.06</v>
       </c>
       <c r="AS2" t="n">
         <v>3.27</v>
@@ -4492,13 +4492,13 @@
         <v>0.41</v>
       </c>
       <c r="AV2" t="n">
-        <v>1.4993458</v>
+        <v>1.3237972</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.698</v>
+        <v>1.5122</v>
       </c>
       <c r="AX2" t="n">
-        <v>2.1395</v>
+        <v>2.058</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -4515,7 +4515,7 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>2953804800</v>
+        <v>2573807104</v>
       </c>
       <c r="BD2" t="n">
         <v>0.12707</v>
@@ -4524,22 +4524,22 @@
         <v>1023101595</v>
       </c>
       <c r="BF2" t="n">
-        <v>2091159353</v>
+        <v>2081305353</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.43265</v>
+        <v>0.42784</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.08790000000000001</v>
+        <v>0.0876</v>
       </c>
       <c r="BI2" t="n">
-        <v>2091159353</v>
+        <v>2081305353</v>
       </c>
       <c r="BJ2" t="n">
-        <v>2.1925685</v>
+        <v>2.191182</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.56554675</v>
+        <v>0.5020122</v>
       </c>
       <c r="BL2" t="n">
         <v>1767139200</v>
@@ -4563,16 +4563,16 @@
         <v>0.22</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.708</v>
+        <v>1.488</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.665</v>
+        <v>6.679</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0.28491622</v>
+        <v>-0.26623374</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BW2" t="n">
         <v>0.01</v>
@@ -4586,19 +4586,19 @@
         </is>
       </c>
       <c r="BZ2" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="CA2" t="n">
-        <v>2.8486075</v>
+        <v>2.8466387</v>
       </c>
       <c r="CB2" t="n">
-        <v>2.8486075</v>
+        <v>2.8466387</v>
       </c>
       <c r="CC2" t="n">
-        <v>2.8486075</v>
+        <v>2.8466387</v>
       </c>
       <c r="CD2" t="n">
-        <v>2.8486075</v>
+        <v>2.8466387</v>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
@@ -4705,144 +4705,144 @@
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>PRE</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
-          <t>VIVA BIOTECH</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>Viva Biotech Holdings</t>
-        </is>
-      </c>
-      <c r="DK2" t="n">
-        <v>-3.1249971</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="DM2" t="n">
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DJ2" t="n">
+        <v>1782115693</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>finmb_595387082</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DN2" t="inlineStr">
+      <c r="DP2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DO2" t="b">
+      <c r="DQ2" t="b">
         <v>0</v>
       </c>
-      <c r="DP2" t="b">
+      <c r="DR2" t="b">
         <v>0</v>
       </c>
-      <c r="DQ2" t="n">
+      <c r="DS2" t="n">
         <v>1557365400000</v>
       </c>
-      <c r="DR2" t="n">
-        <v>-0.03999996</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>1.23 - 1.27</t>
-        </is>
-      </c>
-      <c r="DT2" t="inlineStr">
+      <c r="DT2" t="n">
+        <v>-0.029999971</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>1.08 - 1.14</t>
+        </is>
+      </c>
+      <c r="DV2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DU2" t="n">
-        <v>6502105</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>0.01999998</v>
-      </c>
       <c r="DW2" t="n">
-        <v>0.016393427</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>1.22 - 3.27</t>
-        </is>
+        <v>5444956</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>0.04000008</v>
       </c>
       <c r="DY2" t="n">
-        <v>-2.03</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-0.62079513</v>
+        <v>0.037735928</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>1.06 - 3.27</t>
+        </is>
       </c>
       <c r="EA2" t="n">
-        <v>-28.491623</v>
+        <v>-2.17</v>
       </c>
       <c r="EB2" t="n">
-        <v>1774858200</v>
+        <v>-0.6636086</v>
       </c>
       <c r="EC2" t="n">
-        <v>1774858200</v>
+        <v>-26.623375</v>
       </c>
       <c r="ED2" t="n">
         <v>1774858200</v>
       </c>
-      <c r="EE2" t="b">
+      <c r="EE2" t="n">
+        <v>1774858200</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>1774858200</v>
+      </c>
+      <c r="EG2" t="b">
         <v>0</v>
       </c>
-      <c r="EF2" t="n">
+      <c r="EH2" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="EG2" t="n">
+      <c r="EI2" t="n">
         <v>0.22</v>
       </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EI2" t="n">
-        <v>1780452635</v>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>finmb_595387082</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
+      <c r="EJ2" t="n">
+        <v>-0.41219997</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.27258298</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>-0.95800006</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-0.4655005</v>
       </c>
       <c r="EN2" t="n">
-        <v>-0.45799994</v>
+        <v>15</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0.26972908</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>-0.8994999</v>
-      </c>
-      <c r="EQ2" t="n">
-        <v>-0.4204253</v>
-      </c>
-      <c r="ER2" t="n">
         <v>15</v>
       </c>
+      <c r="EP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>Viva Biotech Holdings</t>
+        </is>
+      </c>
+      <c r="ER2" t="inlineStr">
+        <is>
+          <t>VIVA BIOTECH</t>
+        </is>
+      </c>
       <c r="ES2" t="n">
-        <v>15</v>
-      </c>
-      <c r="ET2" t="b">
-        <v>0</v>
+        <v>-2.6548648</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>1.1</v>
       </c>
       <c r="EU2" t="inlineStr"/>
     </row>
